--- a/AAII_Financials/Yearly/KLAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KLAR_YR_FIN.xlsx
@@ -741,16 +741,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2477000</v>
+        <v>2270000</v>
       </c>
       <c r="E9" s="3">
-        <v>1797000</v>
+        <v>1594000</v>
       </c>
       <c r="F9" s="3">
-        <v>1431000</v>
+        <v>1191000</v>
       </c>
       <c r="G9" s="3">
-        <v>1504000</v>
+        <v>1217000</v>
       </c>
       <c r="H9" s="3">
         <v>596000</v>
@@ -771,16 +771,16 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1032000</v>
+        <v>1239000</v>
       </c>
       <c r="E10" s="3">
-        <v>1014000</v>
+        <v>1217000</v>
       </c>
       <c r="F10" s="3">
-        <v>845000</v>
+        <v>1085000</v>
       </c>
       <c r="G10" s="3">
-        <v>400000</v>
+        <v>687000</v>
       </c>
       <c r="H10" s="3">
         <v>1023700</v>
